--- a/output/pdf_financials_xlsx/NEO.xlsx
+++ b/output/pdf_financials_xlsx/NEO.xlsx
@@ -35698,7 +35698,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">

--- a/output/pdf_financials_xlsx/NEO.xlsx
+++ b/output/pdf_financials_xlsx/NEO.xlsx
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>78.26900000000001</v>
+        <v>88.65900000000001</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>83.069</v>
+        <v>102.07</v>
       </c>
     </row>
     <row r="11">
@@ -6859,10 +6859,10 @@
         </is>
       </c>
       <c r="J124" s="3" t="n">
-        <v>-6.533</v>
+        <v>-8.531000000000001</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>-5</v>
+        <v>-6.427</v>
       </c>
     </row>
     <row r="125">
@@ -6912,10 +6912,10 @@
         </is>
       </c>
       <c r="J125" s="3" t="n">
-        <v>42.668</v>
+        <v>40.67</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>20</v>
+        <v>18.573</v>
       </c>
     </row>
     <row r="126">
@@ -22728,7 +22728,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -35698,7 +35702,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
@@ -36236,7 +36240,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">

--- a/output/pdf_financials_xlsx/NEO.xlsx
+++ b/output/pdf_financials_xlsx/NEO.xlsx
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="J126" s="3" t="n">
-        <v>0</v>
+        <v>-15.183</v>
       </c>
       <c r="K126" s="3" t="n">
-        <v>0</v>
+        <v>-7.343</v>
       </c>
     </row>
     <row r="127">
@@ -22664,7 +22664,11 @@
           <t>Dividends paid to non-controlling interest (Note 23)</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NEO.xlsx
+++ b/output/pdf_financials_xlsx/NEO.xlsx
@@ -3291,13 +3291,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I56" s="3" t="n">
+        <v>265.268</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>289.74</v>
       </c>
       <c r="K56" s="3" t="n">
         <v>0</v>
@@ -3344,13 +3342,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I57" s="3" t="n">
+        <v>86.343</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>91.3</v>
       </c>
       <c r="K57" s="3" t="n">
         <v>0</v>
